--- a/originales/respuestas/2025/01. Calificadas/root/Secretaría Distrital De Planeación.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/root/Secretaría Distrital De Planeación.xlsx
@@ -414,7 +414,7 @@
     <t>¿Su entidad ha puesto a disposición de todos formación orientada al fortalecimiento de capacidades en innovación?</t>
   </si>
   <si>
-    <t>Pregunta 30</t>
+    <t>Pregunta 30.</t>
   </si>
   <si>
     <t>¿Qué estrategias o iniciativas ha implementado su entidad para fomentar una cultura de innovación entre sus funcionarios y contratistas?</t>
@@ -423,7 +423,7 @@
     <t>Incentivos o reconocimientos a iniciativas innovadoras de los funcionarios., Procesos de formación o capacitaciones en metodologías de innovación., Creación de equipos o laboratorios de innovación internos.</t>
   </si>
   <si>
-    <t>Pregunta 31</t>
+    <t>Pregunta 31.</t>
   </si>
   <si>
     <t>¿De qué manera ha incentivado su entidad la participación de los funcionarios y contratistas en procesos de innovación?</t>
@@ -5690,7 +5690,7 @@
       <c r="C18" s="7">
         <v>17.0</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="8" t="s">
         <v>129</v>
       </c>
       <c r="E18" s="6"/>
@@ -5733,7 +5733,7 @@
       <c r="C19" s="11">
         <v>18.0</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="12" t="s">
         <v>132</v>
       </c>
       <c r="E19" s="10"/>
